--- a/revit/ArmadoTrabes_Insurgentes/Correccion_Techos_N11.xlsx
+++ b/revit/ArmadoTrabes_Insurgentes/Correccion_Techos_N11.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3 [S2]</t>
+          <t>T- 7 (viga 1) [T1-3]</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -605,17 +605,17 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J2" s="2" t="n"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>En el plano son vigas separadas: 15X80 con 3#8 (S2) y 15X40 con 2#6 (S1); cada parte se arma aparte. | Plano: 15X80 con 3#8 (dos claros 11@10 @20 11@10; en el modelo son 3 tramos, se puso en cada uno) y 15X40 con 2#6 @10. | secciones: T- EJE 3 Seccion 2 + T- EJE 3 Seccion 1 (se arman juntas; los bastones pasan el cambio de sección)</t>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. | Plano: dos claros 11@10 @20 11@10 y uno @10; en el modelo son 3 tramos + 1: se puso 11@10 @20 11@10 en cada uno (no menos estribos que el plano). | 2 vigas separadas con esta trabe: cada una con sus filas (el paréntesis dice los ejes de sus extremos)</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3 [S2]</t>
+          <t>T- 7 (viga 1) [T1-3]</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -670,17 +670,17 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J3" s="2" t="n"/>
@@ -710,7 +710,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3 [S2]</t>
+          <t>T- 7 (viga 1) [T1-3]</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>15x80</t>
+          <t>15x40</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3#8</t>
+          <t>2#6</t>
         </is>
       </c>
       <c r="J4" s="2" t="n"/>
@@ -771,7 +771,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3 [S1]</t>
+          <t>T- 7 (viga 1) [T4]</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -784,7 +784,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2 (viga)</t>
+          <t>2 (muro)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>En el plano son vigas separadas: 15X80 con 3#8 (S2) y 15X40 con 2#6 (S1); cada parte se arma aparte.</t>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte.</t>
         </is>
       </c>
     </row>
@@ -836,24 +836,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3 [S1]</t>
+          <t>T- 7 (viga 2) [T1-3]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>2 (viga)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>3 (muro bajo la viga)</t>
-        </is>
-      </c>
       <c r="F6" t="n">
-        <v>1.16</v>
+        <v>2.27</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q6" s="2" t="n"/>
@@ -887,7 +887,11 @@
           <t>#3@30</t>
         </is>
       </c>
-      <c r="S6" s="2" t="n"/>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -897,24 +901,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>T- EJE 3 [S1]</t>
+          <t>T- 7 (viga 2) [T1-3]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>3 (muro bajo la viga)</t>
+          <t>2 (viga)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4 (viga)</t>
+          <t>3 (viga)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -939,7 +943,7 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>E#3 @10</t>
+          <t>E#3 11@10 @20 11@10</t>
         </is>
       </c>
       <c r="Q7" s="2" t="n"/>
@@ -949,6 +953,892 @@
         </is>
       </c>
       <c r="S7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>T- 7 (viga 2) [T1-3]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>4 (viga)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>15x40</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>E#3 11@10 @20 11@10</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>T- 7 (viga 2) [T4]</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>15x40</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @10</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>T- EJE 3 [S2]</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3#8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3#8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>E#3 11@10 @20 11@10</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: 15X80 con 3#8 (S2) y 15X40 con 2#6 (S1); cada parte se arma aparte. | Plano: 15X80 con 3#8 (dos claros 11@10 @20 11@10; en el modelo son 3 tramos, se puso en cada uno) y 15X40 con 2#6 @10. | secciones: T- EJE 3 Seccion 2 + T- EJE 3 Seccion 1 (se arman juntas; los bastones pasan el cambio de sección)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>T- EJE 3 [S2]</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3#8</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3#8</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>E#3 11@10 @20 11@10</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>T- EJE 3 [S2]</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>4 (viga)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3#8</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3#8</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>E#3 11@10 @20 11@10</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>T- EJE 3 [S1]</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>1 (viga)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>15x40</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @10</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas: 15X80 con 3#8 (S2) y 15X40 con 2#6 (S1); cada parte se arma aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>T- EJE 3 [S1]</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>3 (muro bajo la viga)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>15x40</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @10</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>T- EJE 3 [S1]</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>3 (muro bajo la viga)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>4 (viga)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>15x40</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2#6</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @10</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>T-EJE K [T1]</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>1 (muro bajo la viga)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2 (muro bajo la viga)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @10</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo 1 (entre los dos cajones) no viene detallado: se supuso @10. | Tramo 1 (entre los dos muros) no viene detallado en el plano: se supuso @10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>T-EJE K [T2-6]</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>1 (muro bajo la viga)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2#6 -100/283</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @10</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>En el plano son vigas separadas (cajones distintos): cada parte se arma aparte. El tramo 1 (entre los dos cajones) no viene detallado: se supuso @10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>T-EJE K [T2-6]</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2 (viga)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3#8 100/225</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1#6 490/225</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>E#3 11@10 @20 11@10</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>T-EJE K [T2-6]</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>3 (viga)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>4 (viga)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>E#3 @10</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>T-EJE K [T2-6]</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>4 (viga)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>5 (viga)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>E#3 11@10 @20 11@10</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Nivel Techos</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>T-EJE K [T2-6]</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>5 (viga)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>6 (viga)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>15x80</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3#6</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>E#3 11@10 @20 11@10</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>#3@30</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S81"/>
